--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -844,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.78</v>
+        <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.78</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>57</v>
       </c>
       <c r="C2" t="n">
-        <v>61.03</v>
+        <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>4.03</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>899</v>
+        <v>2573</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>900</v>
+        <v>2574</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>901</v>
+        <v>2575</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>902</v>
+        <v>2576</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>903</v>
+        <v>2577</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>904</v>
+        <v>2578</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>905</v>
+        <v>2579</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>906</v>
+        <v>2580</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>907</v>
+        <v>2581</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>908</v>
+        <v>2582</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>909</v>
+        <v>2583</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -840,14 +840,24 @@
       <c r="C12" s="2" t="n">
         <v>46153</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G12" t="n">
         <v>10.25</v>
       </c>
       <c r="H12" t="n">
-        <v>10.25</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -860,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>910</v>
+        <v>2584</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -870,14 +880,24 @@
       <c r="C13" s="2" t="n">
         <v>46154</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G13" t="n">
         <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -885,6 +905,306 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2585</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2586</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2587</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2588</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2589</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2590</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2591</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2592</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>8547</v>
       </c>
     </row>
@@ -931,13 +1251,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="C2" t="n">
-        <v>76</v>
+        <v>118.45</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>-14.55</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2573</v>
+        <v>899</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2574</v>
+        <v>900</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2575</v>
+        <v>901</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2576</v>
+        <v>902</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2577</v>
+        <v>903</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2578</v>
+        <v>904</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2579</v>
+        <v>905</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2580</v>
+        <v>906</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2581</v>
+        <v>907</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2582</v>
+        <v>908</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2583</v>
+        <v>909</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -840,24 +840,14 @@
       <c r="C12" s="2" t="n">
         <v>46153</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
       <c r="F12" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>10.25</v>
       </c>
       <c r="H12" t="n">
-        <v>0.75</v>
+        <v>10.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -870,7 +860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2584</v>
+        <v>910</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -880,24 +870,14 @@
       <c r="C13" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
       <c r="F13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -905,306 +885,6 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2585</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2586</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2587</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2588</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2589</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2590</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2591</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>8547</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2592</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PHAN, TIMOTHY T [6153]</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ADMIN2</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
         <v>8547</v>
       </c>
     </row>
@@ -1251,13 +931,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="C2" t="n">
-        <v>118.45</v>
+        <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>-14.55</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>899</v>
+        <v>2573</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>900</v>
+        <v>2574</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>901</v>
+        <v>2575</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>902</v>
+        <v>2576</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>903</v>
+        <v>2577</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>904</v>
+        <v>2578</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>905</v>
+        <v>2579</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>906</v>
+        <v>2580</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>907</v>
+        <v>2581</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>908</v>
+        <v>2582</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>909</v>
+        <v>2583</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -840,14 +840,24 @@
       <c r="C12" s="2" t="n">
         <v>46153</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G12" t="n">
         <v>10.25</v>
       </c>
       <c r="H12" t="n">
-        <v>10.25</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -860,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>910</v>
+        <v>2584</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -870,14 +880,24 @@
       <c r="C13" s="2" t="n">
         <v>46154</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G13" t="n">
         <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -885,6 +905,306 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2585</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2586</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2587</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2588</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2589</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2590</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2591</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2592</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>8547</v>
       </c>
     </row>
@@ -931,13 +1251,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="C2" t="n">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>-10</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1205,46 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2593</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>8547</v>
       </c>
     </row>
@@ -1251,13 +1291,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>133</v>
+        <v>142.5</v>
       </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>127.83</v>
       </c>
       <c r="D2" t="n">
-        <v>-10</v>
+        <v>-14.67</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -1234,10 +1234,10 @@
         <v>9.5</v>
       </c>
       <c r="G22" t="n">
-        <v>4.83</v>
+        <v>9.33</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.67</v>
+        <v>-0.17</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>142.5</v>
       </c>
       <c r="C2" t="n">
-        <v>127.83</v>
+        <v>132.33</v>
       </c>
       <c r="D2" t="n">
-        <v>-14.67</v>
+        <v>-10.17</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2573</v>
+        <v>2542</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2574</v>
+        <v>2543</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2575</v>
+        <v>2544</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2576</v>
+        <v>2545</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2577</v>
+        <v>2546</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2578</v>
+        <v>2547</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2579</v>
+        <v>2548</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2580</v>
+        <v>2549</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2581</v>
+        <v>2550</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2582</v>
+        <v>2551</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2583</v>
+        <v>2552</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2584</v>
+        <v>2553</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2585</v>
+        <v>2554</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2586</v>
+        <v>2555</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2587</v>
+        <v>2556</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2588</v>
+        <v>2557</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2589</v>
+        <v>2558</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2590</v>
+        <v>2559</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2591</v>
+        <v>2560</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2592</v>
+        <v>2561</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2593</v>
+        <v>2562</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1245,6 +1245,266 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2563</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2564</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2565</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2566</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2567</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2568</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2569</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PHAN, TIMOTHY T [6153]</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ADMIN2</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>8547</v>
       </c>
     </row>
@@ -1291,13 +1551,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142.5</v>
+        <v>190</v>
       </c>
       <c r="C2" t="n">
-        <v>132.33</v>
+        <v>161.64</v>
       </c>
       <c r="D2" t="n">
-        <v>-10.17</v>
+        <v>-28.36</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8547.xlsx
+++ b/sheet/8547.xlsx
@@ -1494,10 +1494,10 @@
         <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.62</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.88</v>
+        <v>-0.2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         <v>190</v>
       </c>
       <c r="C2" t="n">
-        <v>161.64</v>
+        <v>166.32</v>
       </c>
       <c r="D2" t="n">
-        <v>-28.36</v>
+        <v>-23.68</v>
       </c>
     </row>
   </sheetData>
